--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80649052-41C4-4F1C-B6A1-89007A7A3840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D73444-7AB5-4C58-846F-5C0184FB6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -710,7 +710,7 @@
         <v>306</v>
       </c>
       <c r="C8" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Program\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D73444-7AB5-4C58-846F-5C0184FB6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A12D275-30F1-48E0-9EF5-7AFA35A10A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32565" yWindow="1710" windowWidth="21600" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -173,11 +173,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -506,7 +505,7 @@
         <v>300</v>
       </c>
       <c r="C2" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -524,10 +523,10 @@
       <c r="H2" s="1">
         <v>-1</v>
       </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
         <v>5</v>
       </c>
     </row>
@@ -540,7 +539,7 @@
         <v>301</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -558,10 +557,10 @@
       <c r="H3" s="1">
         <v>-1</v>
       </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>5</v>
       </c>
     </row>
@@ -574,7 +573,7 @@
         <v>302</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -592,10 +591,10 @@
       <c r="H4" s="1">
         <v>-1</v>
       </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
         <v>5</v>
       </c>
     </row>
@@ -608,7 +607,7 @@
         <v>303</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -626,10 +625,10 @@
       <c r="H5" s="1">
         <v>-1</v>
       </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
         <v>5</v>
       </c>
     </row>
@@ -642,7 +641,7 @@
         <v>304</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -660,10 +659,10 @@
       <c r="H6" s="1">
         <v>-1</v>
       </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>5</v>
       </c>
     </row>
@@ -676,7 +675,7 @@
         <v>305</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
@@ -694,10 +693,10 @@
       <c r="H7" s="1">
         <v>-1</v>
       </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
         <v>5</v>
       </c>
     </row>
@@ -728,10 +727,10 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
         <v>10</v>
       </c>
     </row>
@@ -744,7 +743,7 @@
         <v>307</v>
       </c>
       <c r="C9" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -762,10 +761,10 @@
       <c r="H9" s="1">
         <v>17</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
         <v>10</v>
       </c>
     </row>
@@ -778,7 +777,7 @@
         <v>308</v>
       </c>
       <c r="C10" s="1">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -796,10 +795,10 @@
       <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
         <v>10</v>
       </c>
     </row>
@@ -812,7 +811,7 @@
         <v>309</v>
       </c>
       <c r="C11" s="1">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -830,10 +829,10 @@
       <c r="H11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
         <v>10</v>
       </c>
     </row>
@@ -846,7 +845,7 @@
         <v>310</v>
       </c>
       <c r="C12" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -864,10 +863,10 @@
       <c r="H12" s="1">
         <v>14</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
         <v>10</v>
       </c>
     </row>
@@ -880,7 +879,7 @@
         <v>311</v>
       </c>
       <c r="C13" s="1">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13" s="1">
         <v>6</v>
@@ -898,10 +897,10 @@
       <c r="H13" s="1">
         <v>26</v>
       </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
         <v>10</v>
       </c>
     </row>
@@ -914,7 +913,7 @@
         <v>312</v>
       </c>
       <c r="C14" s="1">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -932,10 +931,10 @@
       <c r="H14" s="1">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
         <v>15</v>
       </c>
     </row>
@@ -948,7 +947,7 @@
         <v>313</v>
       </c>
       <c r="C15" s="1">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -966,10 +965,10 @@
       <c r="H15" s="1">
         <v>16</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
         <v>15</v>
       </c>
     </row>
@@ -982,7 +981,7 @@
         <v>314</v>
       </c>
       <c r="C16" s="1">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -1000,10 +999,10 @@
       <c r="H16" s="1">
         <v>19</v>
       </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
         <v>15</v>
       </c>
     </row>
@@ -1016,7 +1015,7 @@
         <v>315</v>
       </c>
       <c r="C17" s="1">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -1034,10 +1033,10 @@
       <c r="H17" s="1">
         <v>20</v>
       </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
         <v>15</v>
       </c>
     </row>
@@ -1050,7 +1049,7 @@
         <v>316</v>
       </c>
       <c r="C18" s="1">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1">
         <v>5</v>
@@ -1068,10 +1067,10 @@
       <c r="H18" s="1">
         <v>15</v>
       </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>15</v>
       </c>
     </row>
@@ -1084,7 +1083,7 @@
         <v>317</v>
       </c>
       <c r="C19" s="1">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1">
         <v>6</v>
@@ -1102,10 +1101,10 @@
       <c r="H19" s="1">
         <v>1</v>
       </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <v>15</v>
       </c>
     </row>
@@ -1118,7 +1117,7 @@
         <v>318</v>
       </c>
       <c r="C20" s="1">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -1136,10 +1135,10 @@
       <c r="H20" s="1">
         <v>18</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
         <v>20</v>
       </c>
     </row>
@@ -1152,7 +1151,7 @@
         <v>319</v>
       </c>
       <c r="C21" s="1">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -1170,10 +1169,10 @@
       <c r="H21" s="1">
         <v>21</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
         <v>20</v>
       </c>
     </row>
@@ -1186,7 +1185,7 @@
         <v>320</v>
       </c>
       <c r="C22" s="1">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -1204,10 +1203,10 @@
       <c r="H22" s="1">
         <v>22</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
         <v>20</v>
       </c>
     </row>
@@ -1220,7 +1219,7 @@
         <v>321</v>
       </c>
       <c r="C23" s="1">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1">
         <v>4</v>
@@ -1238,15 +1237,15 @@
       <c r="H23" s="1">
         <v>27</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="1">
@@ -1254,7 +1253,7 @@
         <v>322</v>
       </c>
       <c r="C24" s="1">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
@@ -1272,15 +1271,15 @@
       <c r="H24" s="1">
         <v>28</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="1">
@@ -1288,7 +1287,7 @@
         <v>323</v>
       </c>
       <c r="C25" s="1">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1">
         <v>6</v>
@@ -1306,15 +1305,15 @@
       <c r="H25" s="1">
         <v>25</v>
       </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3">
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="1">
@@ -1322,12 +1321,12 @@
         <v>324</v>
       </c>
       <c r="C26" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1">
@@ -1337,18 +1336,18 @@
       <c r="G26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="1">
         <v>-1</v>
       </c>
-      <c r="I26" s="3">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="1">
@@ -1356,12 +1355,12 @@
         <v>325</v>
       </c>
       <c r="C27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D27" s="3">
-        <v>2</v>
-      </c>
-      <c r="E27" s="3">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1">
@@ -1371,18 +1370,18 @@
       <c r="G27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="1">
         <v>-1</v>
       </c>
-      <c r="I27" s="3">
-        <v>1</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="1">
@@ -1390,12 +1389,12 @@
         <v>326</v>
       </c>
       <c r="C28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D28" s="3">
-        <v>3</v>
-      </c>
-      <c r="E28" s="3">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1">
@@ -1405,18 +1404,18 @@
       <c r="G28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="1">
         <v>-1</v>
       </c>
-      <c r="I28" s="3">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3">
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="1">
@@ -1424,12 +1423,12 @@
         <v>327</v>
       </c>
       <c r="C29" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D29" s="3">
-        <v>4</v>
-      </c>
-      <c r="E29" s="3">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1">
+        <v>4</v>
+      </c>
+      <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
@@ -1439,18 +1438,18 @@
       <c r="G29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="1">
         <v>-1</v>
       </c>
-      <c r="I29" s="3">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30" s="1">
@@ -1458,12 +1457,12 @@
         <v>328</v>
       </c>
       <c r="C30" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D30" s="3">
-        <v>5</v>
-      </c>
-      <c r="E30" s="3">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
@@ -1473,18 +1472,18 @@
       <c r="G30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="1">
         <v>-1</v>
       </c>
-      <c r="I30" s="3">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3">
+      <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31" s="1">
@@ -1492,12 +1491,12 @@
         <v>329</v>
       </c>
       <c r="C31" s="1">
-        <v>-1</v>
-      </c>
-      <c r="D31" s="3">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1">
         <v>6</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
@@ -1507,31 +1506,31 @@
       <c r="G31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="1">
         <v>-1</v>
       </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3">
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
         <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="1">
         <f>A32+300</f>
         <v>330</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>-1</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="1">
         <v>6</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="1">
@@ -1541,31 +1540,31 @@
       <c r="G32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="1">
         <v>36</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
       <c r="B33" s="1">
         <f>A33+300</f>
         <v>331</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="1">
         <v>-1</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="1">
         <v>6</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="1">
@@ -1575,13 +1574,13 @@
       <c r="G33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="1">
         <v>36</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
         <v>20</v>
       </c>
     </row>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Program\Droad\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A12D275-30F1-48E0-9EF5-7AFA35A10A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEC77D9-AA1E-4893-947C-32A9FF1317CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32565" yWindow="1710" windowWidth="21600" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -505,7 +505,7 @@
         <v>300</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -539,7 +539,7 @@
         <v>301</v>
       </c>
       <c r="C3" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -573,7 +573,7 @@
         <v>302</v>
       </c>
       <c r="C4" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -607,7 +607,7 @@
         <v>303</v>
       </c>
       <c r="C5" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -641,7 +641,7 @@
         <v>304</v>
       </c>
       <c r="C6" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -675,7 +675,7 @@
         <v>305</v>
       </c>
       <c r="C7" s="1">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>

--- a/Assets/Resources/MasterData/CardData.xlsx
+++ b/Assets/Resources/MasterData/CardData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Droad\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEC77D9-AA1E-4893-947C-32A9FF1317CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E812F73A-A569-421F-AE0B-B6E1713288CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1351,8 +1351,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C27" s="1">
         <v>19</v>
@@ -1385,8 +1384,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C28" s="1">
         <v>19</v>
@@ -1419,8 +1417,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C29" s="1">
         <v>19</v>
@@ -1453,8 +1450,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C30" s="1">
         <v>19</v>
@@ -1487,8 +1483,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C31" s="1">
         <v>19</v>
